--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1603,45 +1603,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1850429</v>
+        <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>75300</v>
+        <v>93417</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6428</v>
+        <v>5965</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lundtaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hydnellum ioeides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Pass.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>400 m SO Skärsviken (03F8e57), Bl</t>
+          <t>Skärsviken, SO om, Bl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523257</v>
+        <v>523200</v>
       </c>
       <c r="R10" t="n">
-        <v>6238353</v>
+        <v>6238411</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1668,17 +1679,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2004-09-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2004-09-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>030584571 / ART VINO / Allmän-riklig (3)  / OBJ.AREA:0,1 ha</t>
+          <t>Återfynd på tidigare känd lokal. Två mindre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,47 +1698,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Grova ädellövträd /</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Gammal grov ek</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
-        </is>
-      </c>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1850429</t>
+          <t>https://artportalen.se/Sighting/136978403</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106309928</v>
+        <v>1850429</v>
       </c>
       <c r="B11" t="n">
-        <v>78685</v>
+        <v>75300</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,37 +1733,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6443</v>
+        <v>6428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>300 m SV Värmansnäs, Bl</t>
+          <t>400 m SO Skärsviken (03F8e57), Bl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523274</v>
+        <v>523257</v>
       </c>
       <c r="R11" t="n">
-        <v>6238225</v>
+        <v>6238353</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,17 +1787,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2004-09-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2004-09-30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På jätteek.</t>
+          <t>030584571 / ART VINO / Allmän-riklig (3)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,67 +1806,74 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
           <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Joakim Andersson Hemberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106309928</t>
+          <t>https://artportalen.se/Sighting/1850429</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106309703</v>
+        <v>106309928</v>
       </c>
       <c r="B12" t="n">
-        <v>9596</v>
+        <v>78685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101479</v>
+        <v>6443</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Osmoderma eremita</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1919,7 +1921,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ganska rikligt med spillning nedanför jätteek i vägkanten.</t>
+          <t>På jätteek.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,63 +1948,60 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106309703</t>
+          <t>https://artportalen.se/Sighting/106309928</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106310589</v>
+        <v>106309703</v>
       </c>
       <c r="B13" t="n">
-        <v>106244</v>
+        <v>9596</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>101479</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Osmoderma eremita</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vid stig mot Skärsviken, Bl</t>
+          <t>300 m SV Värmansnäs, Bl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523201</v>
+        <v>523274</v>
       </c>
       <c r="R13" t="n">
-        <v>6238411</v>
+        <v>6238225</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2037,6 +2036,11 @@
           <t>2023-02-01</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ganska rikligt med spillning nedanför jätteek i vägkanten.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2061,51 +2065,52 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106310589</t>
+          <t>https://artportalen.se/Sighting/106309703</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112358922</v>
+        <v>106310589</v>
       </c>
       <c r="B14" t="n">
-        <v>93195</v>
+        <v>106244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6052576</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Boktaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum fagiscabrosum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>A.M.Ainsw. &amp; Nitare</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2143,12 +2148,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,6 +2179,120 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106310589</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112358922</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6052576</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Boktaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum fagiscabrosum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Nitare</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vid stig mot Skärsviken, Bl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>523201</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6238411</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hjortsberga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112358922</t>
         </is>
@@ -2194,6 +2313,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93419</v>
+        <v>93421</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93421</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93432</v>
+        <v>93434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93434</v>
+        <v>93447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93448</v>
+        <v>93451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93451</v>
+        <v>93461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93461</v>
+        <v>93462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93462</v>
+        <v>93467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93467</v>
+        <v>93469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93469</v>
+        <v>93475</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93475</v>
+        <v>93487</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93487</v>
+        <v>93488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93488</v>
+        <v>93491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 999-2020 artfynd.xlsx
+++ b/artfynd/S 999-2020 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>136978403</v>
       </c>
       <c r="B10" t="n">
-        <v>93492</v>
+        <v>93495</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
